--- a/NURBS IDX30 PYTHON ANALYSIS/Back_final_15_2_26/20gps/7mps_analysis.xlsx
+++ b/NURBS IDX30 PYTHON ANALYSIS/Back_final_15_2_26/20gps/7mps_analysis.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>Time</t>
   </si>
@@ -79,13 +79,34 @@
     <t>Q</t>
   </si>
   <si>
-    <t>rolling_std</t>
-  </si>
-  <si>
     <t>steady_state</t>
   </si>
   <si>
-    <t>avg_Q_steady</t>
+    <t>Averages</t>
+  </si>
+  <si>
+    <t>RTD_OUT_unc</t>
+  </si>
+  <si>
+    <t>RTD_IN_unc</t>
+  </si>
+  <si>
+    <t>RTD_unc</t>
+  </si>
+  <si>
+    <t>Delta_RTD</t>
+  </si>
+  <si>
+    <t>Rel_unc</t>
+  </si>
+  <si>
+    <t>ABS_unc</t>
+  </si>
+  <si>
+    <t>Average Q (W)</t>
+  </si>
+  <si>
+    <t>Average Q Uncertainty (W)</t>
   </si>
 </sst>
 </file>
@@ -421,10 +442,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:AC23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:29">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -497,8 +518,23 @@
       <c r="X1" t="s">
         <v>23</v>
       </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:29">
       <c r="A2" s="1">
         <v>46068.5792018287</v>
       </c>
@@ -562,14 +598,32 @@
       <c r="U2">
         <v>766.7870104738423</v>
       </c>
-      <c r="W2" t="b">
-        <v>0</v>
+      <c r="V2" t="b">
+        <v>1</v>
+      </c>
+      <c r="W2" t="s">
+        <v>29</v>
       </c>
       <c r="X2">
-        <v>756.3550818637028</v>
+        <v>0.244170476</v>
+      </c>
+      <c r="Y2">
+        <v>0.261592312</v>
+      </c>
+      <c r="Z2">
+        <v>0.3578404100259945</v>
+      </c>
+      <c r="AA2">
+        <v>8.710918000000007</v>
+      </c>
+      <c r="AB2">
+        <v>0.04227916409218455</v>
+      </c>
+      <c r="AC2">
+        <v>32.41911383957922</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:29">
       <c r="A3" s="1">
         <v>46068.57931756944</v>
       </c>
@@ -633,11 +687,32 @@
       <c r="U3">
         <v>767.4624662878197</v>
       </c>
-      <c r="W3" t="b">
-        <v>0</v>
+      <c r="V3" t="b">
+        <v>1</v>
+      </c>
+      <c r="W3">
+        <v>760.3749601665666</v>
+      </c>
+      <c r="X3">
+        <v>0.244204762</v>
+      </c>
+      <c r="Y3">
+        <v>0.26159836</v>
+      </c>
+      <c r="Z3">
+        <v>0.357868226779308</v>
+      </c>
+      <c r="AA3">
+        <v>8.696798999999999</v>
+      </c>
+      <c r="AB3">
+        <v>0.04234707417661445</v>
+      </c>
+      <c r="AC3">
+        <v>32.49978998765776</v>
       </c>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:29">
       <c r="A4" s="1">
         <v>46068.57943388889</v>
       </c>
@@ -701,14 +776,32 @@
       <c r="U4">
         <v>767.0937814767309</v>
       </c>
-      <c r="V4">
-        <v>0.3382005063017671</v>
-      </c>
-      <c r="W4" t="b">
+      <c r="V4" t="b">
         <v>1</v>
       </c>
+      <c r="W4" t="s">
+        <v>30</v>
+      </c>
+      <c r="X4">
+        <v>0.244242538</v>
+      </c>
+      <c r="Y4">
+        <v>0.261602496</v>
+      </c>
+      <c r="Z4">
+        <v>0.357897028881369</v>
+      </c>
+      <c r="AA4">
+        <v>8.679979000000003</v>
+      </c>
+      <c r="AB4">
+        <v>0.04242778696072154</v>
+      </c>
+      <c r="AC4">
+        <v>32.54609153938902</v>
+      </c>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:29">
       <c r="A5" s="1">
         <v>46068.57954962963</v>
       </c>
@@ -772,14 +865,32 @@
       <c r="U5">
         <v>767.1336403831749</v>
       </c>
-      <c r="V5">
-        <v>0.2023378766304917</v>
-      </c>
-      <c r="W5" t="b">
+      <c r="V5" t="b">
         <v>1</v>
       </c>
+      <c r="W5">
+        <v>32.48314309845292</v>
+      </c>
+      <c r="X5">
+        <v>0.24424984</v>
+      </c>
+      <c r="Y5">
+        <v>0.26159836</v>
+      </c>
+      <c r="Z5">
+        <v>0.3578989889545865</v>
+      </c>
+      <c r="AA5">
+        <v>8.674259999999997</v>
+      </c>
+      <c r="AB5">
+        <v>0.04245442603498278</v>
+      </c>
+      <c r="AC5">
+        <v>32.56821839459457</v>
+      </c>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:29">
       <c r="A6" s="1">
         <v>46068.57966594907</v>
       </c>
@@ -843,14 +954,29 @@
       <c r="U6">
         <v>765.165753180461</v>
       </c>
-      <c r="V6">
-        <v>1.124830497322734</v>
-      </c>
-      <c r="W6" t="b">
+      <c r="V6" t="b">
         <v>1</v>
       </c>
+      <c r="X6">
+        <v>0.24425714</v>
+      </c>
+      <c r="Y6">
+        <v>0.26159645</v>
+      </c>
+      <c r="Z6">
+        <v>0.3579025748630234</v>
+      </c>
+      <c r="AA6">
+        <v>8.669654999999999</v>
+      </c>
+      <c r="AB6">
+        <v>0.04247612742232644</v>
+      </c>
+      <c r="AC6">
+        <v>32.50127803129364</v>
+      </c>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:29">
       <c r="A7" s="1">
         <v>46068.57978226852</v>
       </c>
@@ -914,14 +1040,29 @@
       <c r="U7">
         <v>765.3506759448458</v>
       </c>
-      <c r="V7">
-        <v>1.086718198655638</v>
-      </c>
-      <c r="W7" t="b">
+      <c r="V7" t="b">
         <v>1</v>
       </c>
+      <c r="X7">
+        <v>0.244248886</v>
+      </c>
+      <c r="Y7">
+        <v>0.26159072</v>
+      </c>
+      <c r="Z7">
+        <v>0.3578927536320893</v>
+      </c>
+      <c r="AA7">
+        <v>8.670917000000003</v>
+      </c>
+      <c r="AB7">
+        <v>0.04246918713201158</v>
+      </c>
+      <c r="AC7">
+        <v>32.50382107831321</v>
+      </c>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:29">
       <c r="A8" s="1">
         <v>46068.57989858797</v>
       </c>
@@ -985,14 +1126,29 @@
       <c r="U8">
         <v>765.9668774652217</v>
       </c>
-      <c r="V8">
-        <v>0.4194641148994795</v>
-      </c>
-      <c r="W8" t="b">
+      <c r="V8" t="b">
         <v>1</v>
       </c>
+      <c r="X8">
+        <v>0.244272696</v>
+      </c>
+      <c r="Y8">
+        <v>0.261583082</v>
+      </c>
+      <c r="Z8">
+        <v>0.3579034210506057</v>
+      </c>
+      <c r="AA8">
+        <v>8.655193000000004</v>
+      </c>
+      <c r="AB8">
+        <v>0.04254326534749888</v>
+      </c>
+      <c r="AC8">
+        <v>32.58673211539809</v>
+      </c>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:29">
       <c r="A9" s="1">
         <v>46068.58001490741</v>
       </c>
@@ -1056,14 +1212,29 @@
       <c r="U9">
         <v>759.8715136431014</v>
       </c>
-      <c r="V9">
-        <v>3.35545287471438</v>
-      </c>
-      <c r="W9" t="b">
-        <v>0</v>
+      <c r="V9" t="b">
+        <v>1</v>
+      </c>
+      <c r="X9">
+        <v>0.244333964</v>
+      </c>
+      <c r="Y9">
+        <v>0.261574806</v>
+      </c>
+      <c r="Z9">
+        <v>0.3579391918998127</v>
+      </c>
+      <c r="AA9">
+        <v>8.620421</v>
+      </c>
+      <c r="AB9">
+        <v>0.04270944200250643</v>
+      </c>
+      <c r="AC9">
+        <v>32.45368834129681</v>
       </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:29">
       <c r="A10" s="1">
         <v>46068.58013064815</v>
       </c>
@@ -1127,14 +1298,29 @@
       <c r="U10">
         <v>758.3806514090828</v>
       </c>
-      <c r="V10">
-        <v>4.019265191956887</v>
-      </c>
-      <c r="W10" t="b">
-        <v>0</v>
+      <c r="V10" t="b">
+        <v>1</v>
+      </c>
+      <c r="X10">
+        <v>0.244362218</v>
+      </c>
+      <c r="Y10">
+        <v>0.261578306</v>
+      </c>
+      <c r="Z10">
+        <v>0.3579610366446453</v>
+      </c>
+      <c r="AA10">
+        <v>8.608044</v>
+      </c>
+      <c r="AB10">
+        <v>0.04276995448561252</v>
+      </c>
+      <c r="AC10">
+        <v>32.43590594353564</v>
       </c>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:29">
       <c r="A11" s="1">
         <v>46068.58024696759</v>
       </c>
@@ -1198,14 +1384,29 @@
       <c r="U11">
         <v>756.6026547858476</v>
       </c>
-      <c r="V11">
-        <v>1.636529886766088</v>
-      </c>
-      <c r="W11" t="b">
+      <c r="V11" t="b">
         <v>1</v>
       </c>
+      <c r="X11">
+        <v>0.244373012</v>
+      </c>
+      <c r="Y11">
+        <v>0.261578306</v>
+      </c>
+      <c r="Z11">
+        <v>0.3579684052591538</v>
+      </c>
+      <c r="AA11">
+        <v>8.602646999999997</v>
+      </c>
+      <c r="AB11">
+        <v>0.04279615329831042</v>
+      </c>
+      <c r="AC11">
+        <v>32.37968320012377</v>
+      </c>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:29">
       <c r="A12" s="1">
         <v>46068.58036328704</v>
       </c>
@@ -1269,14 +1470,29 @@
       <c r="U12">
         <v>764.3761742507671</v>
       </c>
-      <c r="V12">
-        <v>4.072983570816524</v>
-      </c>
-      <c r="W12" t="b">
-        <v>0</v>
+      <c r="V12" t="b">
+        <v>1</v>
+      </c>
+      <c r="X12">
+        <v>0.244376504</v>
+      </c>
+      <c r="Y12">
+        <v>0.261569394</v>
+      </c>
+      <c r="Z12">
+        <v>0.3579642769673941</v>
+      </c>
+      <c r="AA12">
+        <v>8.596445000000003</v>
+      </c>
+      <c r="AB12">
+        <v>0.04282487686487577</v>
+      </c>
+      <c r="AC12">
+        <v>32.73431554073392</v>
       </c>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:29">
       <c r="A13" s="1">
         <v>46068.58047902778</v>
       </c>
@@ -1340,14 +1556,29 @@
       <c r="U13">
         <v>757.6199374081791</v>
       </c>
-      <c r="V13">
-        <v>4.225107593862636</v>
-      </c>
-      <c r="W13" t="b">
-        <v>0</v>
+      <c r="V13" t="b">
+        <v>1</v>
+      </c>
+      <c r="X13">
+        <v>0.244348884</v>
+      </c>
+      <c r="Y13">
+        <v>0.261568122</v>
+      </c>
+      <c r="Z13">
+        <v>0.3579444922870756</v>
+      </c>
+      <c r="AA13">
+        <v>8.609619000000002</v>
+      </c>
+      <c r="AB13">
+        <v>0.04276068979258587</v>
+      </c>
+      <c r="AC13">
+        <v>32.39635112418947</v>
       </c>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:29">
       <c r="A14" s="1">
         <v>46068.58059534722</v>
       </c>
@@ -1411,14 +1642,29 @@
       <c r="U14">
         <v>759.2422501820644</v>
       </c>
-      <c r="V14">
-        <v>3.526939451153853</v>
-      </c>
-      <c r="W14" t="b">
-        <v>0</v>
+      <c r="V14" t="b">
+        <v>1</v>
+      </c>
+      <c r="X14">
+        <v>0.244383804</v>
+      </c>
+      <c r="Y14">
+        <v>0.26157226</v>
+      </c>
+      <c r="Z14">
+        <v>0.3579713548023333</v>
+      </c>
+      <c r="AA14">
+        <v>8.594228000000001</v>
+      </c>
+      <c r="AB14">
+        <v>0.04283612263954205</v>
+      </c>
+      <c r="AC14">
+        <v>32.52299414192078</v>
       </c>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:29">
       <c r="A15" s="1">
         <v>46068.58071108796</v>
       </c>
@@ -1482,14 +1728,29 @@
       <c r="U15">
         <v>756.2737816586146</v>
       </c>
-      <c r="V15">
-        <v>1.486373630298206</v>
-      </c>
-      <c r="W15" t="b">
+      <c r="V15" t="b">
         <v>1</v>
       </c>
+      <c r="X15">
+        <v>0.24438063</v>
+      </c>
+      <c r="Y15">
+        <v>0.261559846</v>
+      </c>
+      <c r="Z15">
+        <v>0.3579601169945342</v>
+      </c>
+      <c r="AA15">
+        <v>8.589607999999998</v>
+      </c>
+      <c r="AB15">
+        <v>0.04285663495249049</v>
+      </c>
+      <c r="AC15">
+        <v>32.41134938468274</v>
+      </c>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:29">
       <c r="A16" s="1">
         <v>46068.58082740741</v>
       </c>
@@ -1553,14 +1814,29 @@
       <c r="U16">
         <v>756.9511406881496</v>
       </c>
-      <c r="V16">
-        <v>1.55562438389844</v>
-      </c>
-      <c r="W16" t="b">
+      <c r="V16" t="b">
         <v>1</v>
       </c>
+      <c r="X16">
+        <v>0.244406028</v>
+      </c>
+      <c r="Y16">
+        <v>0.26154775</v>
+      </c>
+      <c r="Z16">
+        <v>0.3579686188100841</v>
+      </c>
+      <c r="AA16">
+        <v>8.570860999999994</v>
+      </c>
+      <c r="AB16">
+        <v>0.04294624124507415</v>
+      </c>
+      <c r="AC16">
+        <v>32.50820629872734</v>
+      </c>
     </row>
-    <row r="17" spans="1:23">
+    <row r="17" spans="1:29">
       <c r="A17" s="1">
         <v>46068.58094372685</v>
       </c>
@@ -1624,14 +1900,29 @@
       <c r="U17">
         <v>755.5705520650862</v>
       </c>
-      <c r="V17">
-        <v>0.6903347089395444</v>
-      </c>
-      <c r="W17" t="b">
+      <c r="V17" t="b">
         <v>1</v>
       </c>
+      <c r="X17">
+        <v>0.244380948</v>
+      </c>
+      <c r="Y17">
+        <v>0.261535974</v>
+      </c>
+      <c r="Z17">
+        <v>0.3579428913129962</v>
+      </c>
+      <c r="AA17">
+        <v>8.577512999999996</v>
+      </c>
+      <c r="AB17">
+        <v>0.04291182534859361</v>
+      </c>
+      <c r="AC17">
+        <v>32.42291156875743</v>
+      </c>
     </row>
-    <row r="18" spans="1:23">
+    <row r="18" spans="1:29">
       <c r="A18" s="1">
         <v>46068.58105946759</v>
       </c>
@@ -1695,14 +1986,29 @@
       <c r="U18">
         <v>759.3507516697572</v>
       </c>
-      <c r="V18">
-        <v>1.912854187695432</v>
-      </c>
-      <c r="W18" t="b">
+      <c r="V18" t="b">
         <v>1</v>
       </c>
+      <c r="X18">
+        <v>0.24434317</v>
+      </c>
+      <c r="Y18">
+        <v>0.26153279</v>
+      </c>
+      <c r="Z18">
+        <v>0.3579147733341458</v>
+      </c>
+      <c r="AA18">
+        <v>8.594810000000003</v>
+      </c>
+      <c r="AB18">
+        <v>0.04282697880069205</v>
+      </c>
+      <c r="AC18">
+        <v>32.52069854405026</v>
+      </c>
     </row>
-    <row r="19" spans="1:23">
+    <row r="19" spans="1:29">
       <c r="A19" s="1">
         <v>46068.58117520833</v>
       </c>
@@ -1766,14 +2072,29 @@
       <c r="U19">
         <v>758.3093031077476</v>
       </c>
-      <c r="V19">
-        <v>1.952574430169594</v>
-      </c>
-      <c r="W19" t="b">
+      <c r="V19" t="b">
         <v>1</v>
       </c>
+      <c r="X19">
+        <v>0.24435079</v>
+      </c>
+      <c r="Y19">
+        <v>0.26152929</v>
+      </c>
+      <c r="Z19">
+        <v>0.357917417991257</v>
+      </c>
+      <c r="AA19">
+        <v>8.58925</v>
+      </c>
+      <c r="AB19">
+        <v>0.04285348997975409</v>
+      </c>
+      <c r="AC19">
+        <v>32.49620012228217</v>
+      </c>
     </row>
-    <row r="20" spans="1:23">
+    <row r="20" spans="1:29">
       <c r="A20" s="1">
         <v>46068.58129152778</v>
       </c>
@@ -1837,14 +2158,29 @@
       <c r="U20">
         <v>753.5570496684941</v>
       </c>
-      <c r="V20">
-        <v>3.0885679188909</v>
-      </c>
-      <c r="W20" t="b">
-        <v>0</v>
+      <c r="V20" t="b">
+        <v>1</v>
+      </c>
+      <c r="X20">
+        <v>0.244368884</v>
+      </c>
+      <c r="Y20">
+        <v>0.261528334</v>
+      </c>
+      <c r="Z20">
+        <v>0.3579290725160796</v>
+      </c>
+      <c r="AA20">
+        <v>8.579725000000003</v>
+      </c>
+      <c r="AB20">
+        <v>0.04289979655864277</v>
+      </c>
+      <c r="AC20">
+        <v>32.32744412610946</v>
       </c>
     </row>
-    <row r="21" spans="1:23">
+    <row r="21" spans="1:29">
       <c r="A21" s="1">
         <v>46068.58140726852</v>
       </c>
@@ -1908,14 +2244,29 @@
       <c r="U21">
         <v>754.6783971431739</v>
       </c>
-      <c r="V21">
-        <v>2.484109868524325</v>
-      </c>
-      <c r="W21" t="b">
+      <c r="V21" t="b">
         <v>1</v>
       </c>
+      <c r="X21">
+        <v>0.24437936</v>
+      </c>
+      <c r="Y21">
+        <v>0.261514648</v>
+      </c>
+      <c r="Z21">
+        <v>0.3579262252372317</v>
+      </c>
+      <c r="AA21">
+        <v>8.567643999999994</v>
+      </c>
+      <c r="AB21">
+        <v>0.04295668047746477</v>
+      </c>
+      <c r="AC21">
+        <v>32.41847876932458</v>
+      </c>
     </row>
-    <row r="22" spans="1:23">
+    <row r="22" spans="1:29">
       <c r="A22" s="1">
         <v>46068.58152300926</v>
       </c>
@@ -1979,14 +2330,29 @@
       <c r="U22">
         <v>754.9529097781154</v>
       </c>
-      <c r="V22">
-        <v>0.7395046530499942</v>
-      </c>
-      <c r="W22" t="b">
+      <c r="V22" t="b">
         <v>1</v>
       </c>
+      <c r="X22">
+        <v>0.244368566</v>
+      </c>
+      <c r="Y22">
+        <v>0.261504144</v>
+      </c>
+      <c r="Z22">
+        <v>0.3579111808508769</v>
+      </c>
+      <c r="AA22">
+        <v>8.567788999999998</v>
+      </c>
+      <c r="AB22">
+        <v>0.04295428520381198</v>
+      </c>
+      <c r="AC22">
+        <v>32.4284626020569</v>
+      </c>
     </row>
-    <row r="23" spans="1:23">
+    <row r="23" spans="1:29">
       <c r="A23" s="1">
         <v>46068.58163875</v>
       </c>
@@ -2050,11 +2416,26 @@
       <c r="U23">
         <v>757.5518509941866</v>
       </c>
-      <c r="V23">
-        <v>1.585695938969763</v>
-      </c>
-      <c r="W23" t="b">
+      <c r="V23" t="b">
         <v>1</v>
+      </c>
+      <c r="X23">
+        <v>0.244360314</v>
+      </c>
+      <c r="Y23">
+        <v>0.261491094</v>
+      </c>
+      <c r="Z23">
+        <v>0.3578960118519001</v>
+      </c>
+      <c r="AA23">
+        <v>8.565390000000001</v>
+      </c>
+      <c r="AB23">
+        <v>0.04296394158265642</v>
+      </c>
+      <c r="AC23">
+        <v>32.54741347194747</v>
       </c>
     </row>
   </sheetData>
